--- a/doorpass/public/buildings_template_sub_admin.xlsx
+++ b/doorpass/public/buildings_template_sub_admin.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>건물명</t>
   </si>
@@ -34,6 +34,9 @@
     <t>메모</t>
   </si>
   <si>
+    <t>출입방식</t>
+  </si>
+  <si>
     <t>신정마을아파트</t>
   </si>
   <si>
@@ -47,6 +50,9 @@
   </si>
   <si>
     <t>1동 출입구</t>
+  </si>
+  <si>
+    <t>password</t>
   </si>
 </sst>
 </file>
@@ -423,7 +429,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -431,9 +437,10 @@
     <col min="3" max="3" width="14" customWidth="1"/>
     <col min="4" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="24" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -455,16 +462,19 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>35.5384</v>
@@ -473,10 +483,13 @@
         <v>129.3114</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="H2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
